--- a/data/trans_orig/ESTUDIOS-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2007</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52928</t>
+          <t>52519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84627</t>
+          <t>82233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>42605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>72190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103985</t>
+          <t>104149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146090</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>322310</t>
+          <t>323760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>375273</t>
+          <t>379147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286632</t>
+          <t>285908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339801</t>
+          <t>338587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>627461</t>
+          <t>622677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>698041</t>
+          <t>697814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>253288</t>
+          <t>250160</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>304010</t>
+          <t>300784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>295036</t>
+          <t>293671</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>347332</t>
+          <t>344129</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>561975</t>
+          <t>564629</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>632616</t>
+          <t>636140</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103098</t>
+          <t>103814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147605</t>
+          <t>146615</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97676</t>
+          <t>96860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138380</t>
+          <t>136903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211195</t>
+          <t>212106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>270662</t>
+          <t>269899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>454865</t>
+          <t>458504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>522084</t>
+          <t>518429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>424243</t>
+          <t>423873</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>488641</t>
+          <t>481219</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>897241</t>
+          <t>903231</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>990060</t>
+          <t>990718</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>320270</t>
+          <t>318254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>384113</t>
+          <t>377883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>364578</t>
+          <t>370583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>428505</t>
+          <t>431417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>702499</t>
+          <t>703405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>791546</t>
+          <t>789445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113059</t>
+          <t>113142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158271</t>
+          <t>159276</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72763</t>
+          <t>72323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>107881</t>
+          <t>106394</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>196210</t>
+          <t>193499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>252091</t>
+          <t>251058</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>330571</t>
+          <t>331653</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>384390</t>
+          <t>385612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>306740</t>
+          <t>310550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>359860</t>
+          <t>359031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>655901</t>
+          <t>660543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>732923</t>
+          <t>728877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161472</t>
+          <t>161131</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209477</t>
+          <t>207497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>236685</t>
+          <t>236447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>286917</t>
+          <t>286449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>409817</t>
+          <t>413864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>477327</t>
+          <t>480901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>200129</t>
+          <t>199146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>253569</t>
+          <t>251443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191738</t>
+          <t>190601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245488</t>
+          <t>243154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>406499</t>
+          <t>403023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>480318</t>
+          <t>476860</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>465580</t>
+          <t>463545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525712</t>
+          <t>525630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>453877</t>
+          <t>452804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>517633</t>
+          <t>520844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938353</t>
+          <t>936177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1026450</t>
+          <t>1026092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196855</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>246981</t>
+          <t>248093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>306831</t>
+          <t>305526</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>364965</t>
+          <t>367445</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>519016</t>
+          <t>519053</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>595426</t>
+          <t>595523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>504486</t>
+          <t>509292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>593968</t>
+          <t>600239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>438292</t>
+          <t>438952</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>520395</t>
+          <t>516263</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>973294</t>
+          <t>966748</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1091586</t>
+          <t>1094736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1635903</t>
+          <t>1627685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1751126</t>
+          <t>1750356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1529325</t>
+          <t>1530722</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1646395</t>
+          <t>1646221</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3190490</t>
+          <t>3194336</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3359739</t>
+          <t>3362410</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>973795</t>
+          <t>983225</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1084056</t>
+          <t>1088008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1254028</t>
+          <t>1252523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1366719</t>
+          <t>1367276</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2267662</t>
+          <t>2259779</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2423993</t>
+          <t>2412654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2012</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46310</t>
+          <t>47093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78405</t>
+          <t>79802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52254</t>
+          <t>51122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84767</t>
+          <t>83982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105081</t>
+          <t>107706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>149872</t>
+          <t>154835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361877</t>
+          <t>361423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415449</t>
+          <t>414398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305112</t>
+          <t>302740</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>356310</t>
+          <t>357825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682923</t>
+          <t>680422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>755445</t>
+          <t>755455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>226198</t>
+          <t>226973</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>278554</t>
+          <t>278585</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>274229</t>
+          <t>272990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>327559</t>
+          <t>326273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>517246</t>
+          <t>515469</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>589536</t>
+          <t>589592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99946</t>
+          <t>100982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>144730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78395</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118349</t>
+          <t>117050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189591</t>
+          <t>190451</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249852</t>
+          <t>247795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>545740</t>
+          <t>543304</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>611694</t>
+          <t>613325</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>494049</t>
+          <t>498142</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>564138</t>
+          <t>563630</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1060496</t>
+          <t>1061358</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1156057</t>
+          <t>1154287</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285093</t>
+          <t>285957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>346561</t>
+          <t>346281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372196</t>
+          <t>372726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>437810</t>
+          <t>436310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>674632</t>
+          <t>676528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>766526</t>
+          <t>764763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84942</t>
+          <t>85636</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126544</t>
+          <t>126998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83574</t>
+          <t>82455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123742</t>
+          <t>124287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>181846</t>
+          <t>178430</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>237600</t>
+          <t>241229</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>415158</t>
+          <t>413983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>468401</t>
+          <t>469213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>361780</t>
+          <t>364712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>419893</t>
+          <t>423172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>796308</t>
+          <t>796432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>878447</t>
+          <t>877700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182951</t>
+          <t>183776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233532</t>
+          <t>235887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255185</t>
+          <t>253978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>311971</t>
+          <t>308692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>451754</t>
+          <t>450144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>529988</t>
+          <t>523361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167445</t>
+          <t>167590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>219728</t>
+          <t>219273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166188</t>
+          <t>167897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220904</t>
+          <t>218596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>352489</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>422540</t>
+          <t>426618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>523667</t>
+          <t>523133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>584443</t>
+          <t>583184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>470217</t>
+          <t>472207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535362</t>
+          <t>540886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1016031</t>
+          <t>1015415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1105349</t>
+          <t>1105671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173461</t>
+          <t>175479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225597</t>
+          <t>226006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>322257</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>383417</t>
+          <t>381036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>509266</t>
+          <t>508840</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>588730</t>
+          <t>591034</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>435808</t>
+          <t>441643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>520932</t>
+          <t>524800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>418653</t>
+          <t>416935</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>497333</t>
+          <t>497515</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>879508</t>
+          <t>883662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1000252</t>
+          <t>1003061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1905733</t>
+          <t>1904778</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2025050</t>
+          <t>2023077</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1696621</t>
+          <t>1699465</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1815997</t>
+          <t>1818182</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3635073</t>
+          <t>3635571</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3803877</t>
+          <t>3806724</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>925115</t>
+          <t>919538</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1030407</t>
+          <t>1034254</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1275324</t>
+          <t>1276796</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1390487</t>
+          <t>1394574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2236082</t>
+          <t>2228586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2391923</t>
+          <t>2393811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2016</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43851</t>
+          <t>43023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73781</t>
+          <t>73909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45914</t>
+          <t>45633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73582</t>
+          <t>73241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95459</t>
+          <t>95263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139130</t>
+          <t>137254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368678</t>
+          <t>369813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420216</t>
+          <t>418875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>341663</t>
+          <t>341083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390638</t>
+          <t>394313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>723982</t>
+          <t>718676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>798021</t>
+          <t>797472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>196841</t>
+          <t>196234</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>245416</t>
+          <t>244030</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>222035</t>
+          <t>220040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>269873</t>
+          <t>270717</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>430269</t>
+          <t>429907</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>500941</t>
+          <t>502535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117468</t>
+          <t>117359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161961</t>
+          <t>163494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125937</t>
+          <t>127876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171657</t>
+          <t>176345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>257344</t>
+          <t>256192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322302</t>
+          <t>321061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>593248</t>
+          <t>595271</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>655695</t>
+          <t>657842</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>533981</t>
+          <t>538189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>605839</t>
+          <t>603471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1146034</t>
+          <t>1147155</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1240951</t>
+          <t>1239627</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,36%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225868</t>
+          <t>223938</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>280624</t>
+          <t>278814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>287312</t>
+          <t>287473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>350384</t>
+          <t>348173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>528634</t>
+          <t>528153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>610866</t>
+          <t>607089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83338</t>
+          <t>82813</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122513</t>
+          <t>124331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88237</t>
+          <t>85418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>127009</t>
+          <t>125842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179797</t>
+          <t>181200</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>233225</t>
+          <t>237823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>488973</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>544352</t>
+          <t>540988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>458682</t>
+          <t>459163</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514466</t>
+          <t>513480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>966300</t>
+          <t>960477</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1039207</t>
+          <t>1041314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121876</t>
+          <t>121894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163761</t>
+          <t>164030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168847</t>
+          <t>169302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>218944</t>
+          <t>219985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302266</t>
+          <t>299524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366846</t>
+          <t>366669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>221602</t>
+          <t>221698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>277976</t>
+          <t>277274</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>209647</t>
+          <t>211034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>265885</t>
+          <t>265451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>445853</t>
+          <t>448651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>523555</t>
+          <t>530423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>511284</t>
+          <t>511955</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>571168</t>
+          <t>571549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>528240</t>
+          <t>531672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>595967</t>
+          <t>598029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058994</t>
+          <t>1056454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1153037</t>
+          <t>1148933</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118764</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>161591</t>
+          <t>162523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210847</t>
+          <t>210092</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>271105</t>
+          <t>266254</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>345468</t>
+          <t>344769</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>418004</t>
+          <t>420739</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>503587</t>
+          <t>505598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>592799</t>
+          <t>592706</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>504970</t>
+          <t>503545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>597590</t>
+          <t>590770</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1037197</t>
+          <t>1043913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1157595</t>
+          <t>1163837</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2024470</t>
+          <t>2019681</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2136866</t>
+          <t>2137122</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1929646</t>
+          <t>1927529</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2051783</t>
+          <t>2048841</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3973205</t>
+          <t>3989228</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4138121</t>
+          <t>4149508</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>708414</t>
+          <t>701210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>801609</t>
+          <t>799716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>940730</t>
+          <t>939460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1055023</t>
+          <t>1053606</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1677152</t>
+          <t>1675399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1822310</t>
+          <t>1818983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2023</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64364</t>
+          <t>63651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102151</t>
+          <t>100995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72595</t>
+          <t>72701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99313</t>
+          <t>101602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143718</t>
+          <t>143202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190292</t>
+          <t>190684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>370802</t>
+          <t>372138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420713</t>
+          <t>421517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>380882</t>
+          <t>379590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420030</t>
+          <t>418468</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>762386</t>
+          <t>763222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>825647</t>
+          <t>829529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,38%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>138934</t>
+          <t>139110</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>181161</t>
+          <t>179524</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171312</t>
+          <t>172424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>206133</t>
+          <t>206049</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>322057</t>
+          <t>321649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>375138</t>
+          <t>374855</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84265</t>
+          <t>80107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219334</t>
+          <t>224058</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145984</t>
+          <t>145024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>185460</t>
+          <t>183957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>227366</t>
+          <t>212935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>383870</t>
+          <t>387312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>761759</t>
+          <t>761433</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1012256</t>
+          <t>1040836</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>550580</t>
+          <t>550602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>601339</t>
+          <t>599128</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1327264</t>
+          <t>1325008</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1665640</t>
+          <t>1674198</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89844</t>
+          <t>75542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221645</t>
+          <t>220502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199022</t>
+          <t>197663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238428</t>
+          <t>239139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>251012</t>
+          <t>259383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>449888</t>
+          <t>448108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109803</t>
+          <t>109780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156794</t>
+          <t>156312</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80383</t>
+          <t>74581</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>196646</t>
+          <t>195265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>188920</t>
+          <t>171483</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329909</t>
+          <t>325458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>466423</t>
+          <t>467270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518896</t>
+          <t>519716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>559709</t>
+          <t>563505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>783085</t>
+          <t>791254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1064795</t>
+          <t>1067292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1302612</t>
+          <t>1324478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61442</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93442</t>
+          <t>92854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68823</t>
+          <t>67217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>181512</t>
+          <t>179600</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142401</t>
+          <t>138121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250444</t>
+          <t>249912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>241053</t>
+          <t>241728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>297879</t>
+          <t>298402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221018</t>
+          <t>213820</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>299056</t>
+          <t>299303</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>473383</t>
+          <t>467157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>581991</t>
+          <t>578710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>508696</t>
+          <t>511264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>572221</t>
+          <t>571760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>565124</t>
+          <t>562776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>698432</t>
+          <t>708381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1093946</t>
+          <t>1100485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1253069</t>
+          <t>1254691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,34%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92011</t>
+          <t>94070</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131649</t>
+          <t>130589</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166921</t>
+          <t>173757</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241547</t>
+          <t>243734</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>283478</t>
+          <t>288641</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>356618</t>
+          <t>361077</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>501443</t>
+          <t>506288</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>718854</t>
+          <t>714052</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>540195</t>
+          <t>534566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>721328</t>
+          <t>724014</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1124701</t>
+          <t>1142504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1416665</t>
+          <t>1412003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2184617</t>
+          <t>2180364</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2548430</t>
+          <t>2546506</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2118079</t>
+          <t>2123130</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2504404</t>
+          <t>2513248</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,47 +10256,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>4528150</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>4342465</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>4870359</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>63,73%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>61,11%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>68,54%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>4913</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>4528150</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>4338019</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>4883446</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>61,05%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>400712</t>
+          <t>400690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>570666</t>
+          <t>574038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>612161</t>
+          <t>616359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>826788</t>
+          <t>820730</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1092163</t>
+          <t>1099221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1366081</t>
+          <t>1372437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ESTUDIOS-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52519</t>
+          <t>53135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82233</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42605</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>70714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104149</t>
+          <t>104403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147134</t>
+          <t>145888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323760</t>
+          <t>323520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379147</t>
+          <t>376812</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285908</t>
+          <t>284964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338587</t>
+          <t>337578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>622677</t>
+          <t>625114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>697814</t>
+          <t>700805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>250160</t>
+          <t>251291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300784</t>
+          <t>302296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>293671</t>
+          <t>293188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>344129</t>
+          <t>346481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>564629</t>
+          <t>561285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>636140</t>
+          <t>630945</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103814</t>
+          <t>101503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146615</t>
+          <t>146487</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96860</t>
+          <t>96573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136903</t>
+          <t>138502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212106</t>
+          <t>209149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269899</t>
+          <t>271304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>458504</t>
+          <t>457129</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518429</t>
+          <t>519316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>423873</t>
+          <t>422956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>481219</t>
+          <t>486797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>903231</t>
+          <t>895318</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>990718</t>
+          <t>992125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>318254</t>
+          <t>320632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>377883</t>
+          <t>379107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>370583</t>
+          <t>364200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>431417</t>
+          <t>427222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>703405</t>
+          <t>704273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>789445</t>
+          <t>791074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113142</t>
+          <t>113666</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159276</t>
+          <t>158444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72323</t>
+          <t>68983</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106394</t>
+          <t>105852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>193499</t>
+          <t>194942</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251058</t>
+          <t>249443</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>331653</t>
+          <t>332637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>385612</t>
+          <t>386714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310550</t>
+          <t>308353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>359031</t>
+          <t>360978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>660543</t>
+          <t>658738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>728877</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161131</t>
+          <t>161728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207497</t>
+          <t>209379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>236447</t>
+          <t>235032</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>286449</t>
+          <t>286202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413864</t>
+          <t>409629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>480901</t>
+          <t>476616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199146</t>
+          <t>201486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>251443</t>
+          <t>253030</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190601</t>
+          <t>189192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243154</t>
+          <t>245391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>403023</t>
+          <t>403863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>476860</t>
+          <t>480223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463545</t>
+          <t>466270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525630</t>
+          <t>526824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452804</t>
+          <t>452147</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520844</t>
+          <t>517803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>936177</t>
+          <t>937826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1026092</t>
+          <t>1021714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196441</t>
+          <t>196210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>248093</t>
+          <t>244566</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>305526</t>
+          <t>305901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>367445</t>
+          <t>364839</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>519053</t>
+          <t>520817</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>595523</t>
+          <t>598916</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>509292</t>
+          <t>510725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>600239</t>
+          <t>598849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>438952</t>
+          <t>439315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>516263</t>
+          <t>520038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>966748</t>
+          <t>972865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1094736</t>
+          <t>1087365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1627685</t>
+          <t>1634483</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1750356</t>
+          <t>1749045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1530722</t>
+          <t>1526643</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1646221</t>
+          <t>1645457</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3194336</t>
+          <t>3202345</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3362410</t>
+          <t>3360901</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>983225</t>
+          <t>981453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1088008</t>
+          <t>1084128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1252523</t>
+          <t>1259040</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1367276</t>
+          <t>1371631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2259779</t>
+          <t>2270234</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2412654</t>
+          <t>2424643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47093</t>
+          <t>47280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79802</t>
+          <t>79882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51122</t>
+          <t>50877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83982</t>
+          <t>84301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107706</t>
+          <t>107838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154835</t>
+          <t>151793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361423</t>
+          <t>364606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>416106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>302740</t>
+          <t>303822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357825</t>
+          <t>357680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680422</t>
+          <t>680349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>755455</t>
+          <t>758398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>227378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>278585</t>
+          <t>275977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>272990</t>
+          <t>273104</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>326273</t>
+          <t>325682</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>515469</t>
+          <t>513345</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>589592</t>
+          <t>591771</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100982</t>
+          <t>98780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144730</t>
+          <t>144226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78072</t>
+          <t>76285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117050</t>
+          <t>118901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>190451</t>
+          <t>191026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>247795</t>
+          <t>249091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>543304</t>
+          <t>546449</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>613325</t>
+          <t>613129</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>498142</t>
+          <t>499635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>563630</t>
+          <t>567171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1061358</t>
+          <t>1067774</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1154287</t>
+          <t>1159324</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285957</t>
+          <t>284513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>346281</t>
+          <t>346377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372726</t>
+          <t>371023</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>436310</t>
+          <t>435201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>676528</t>
+          <t>672247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>764763</t>
+          <t>764648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85636</t>
+          <t>85628</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126998</t>
+          <t>127808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82455</t>
+          <t>84793</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124287</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>178430</t>
+          <t>179365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>241229</t>
+          <t>243767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>413983</t>
+          <t>412957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>469213</t>
+          <t>468823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>364712</t>
+          <t>363161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>423172</t>
+          <t>420347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>796432</t>
+          <t>795484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>877700</t>
+          <t>874090</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183776</t>
+          <t>185352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235887</t>
+          <t>236501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>253978</t>
+          <t>254150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>308692</t>
+          <t>311703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>450144</t>
+          <t>451529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>523361</t>
+          <t>525225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167590</t>
+          <t>166328</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>219273</t>
+          <t>218537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167897</t>
+          <t>165719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218596</t>
+          <t>218418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>352489</t>
+          <t>348764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>426618</t>
+          <t>422401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>523133</t>
+          <t>523033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>583184</t>
+          <t>585334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>470847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540886</t>
+          <t>536254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1015415</t>
+          <t>1011967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1105671</t>
+          <t>1104746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>175479</t>
+          <t>175034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>226006</t>
+          <t>225328</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>320832</t>
+          <t>322082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>381036</t>
+          <t>384994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>508840</t>
+          <t>508616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>591034</t>
+          <t>593551</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>441643</t>
+          <t>440170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>524800</t>
+          <t>520178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>416935</t>
+          <t>419779</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>497515</t>
+          <t>500177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>883662</t>
+          <t>881610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1003061</t>
+          <t>1002585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1904778</t>
+          <t>1903962</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2023077</t>
+          <t>2025145</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1699465</t>
+          <t>1696572</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1818182</t>
+          <t>1822178</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3635571</t>
+          <t>3632840</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3806724</t>
+          <t>3810155</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>919538</t>
+          <t>918790</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1034254</t>
+          <t>1028475</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1276796</t>
+          <t>1272847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1394574</t>
+          <t>1397965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2228586</t>
+          <t>2232955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2393811</t>
+          <t>2397915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43023</t>
+          <t>43458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73909</t>
+          <t>73510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45633</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73241</t>
+          <t>74557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95263</t>
+          <t>94735</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137254</t>
+          <t>138297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>369813</t>
+          <t>366936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418875</t>
+          <t>419398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>341083</t>
+          <t>341358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394313</t>
+          <t>390242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>718676</t>
+          <t>725831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>797472</t>
+          <t>797153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>196234</t>
+          <t>194393</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244030</t>
+          <t>243914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>220040</t>
+          <t>221953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>270717</t>
+          <t>272411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>429907</t>
+          <t>432605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>502535</t>
+          <t>500741</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117359</t>
+          <t>116450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163494</t>
+          <t>163517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>127876</t>
+          <t>127218</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176345</t>
+          <t>172368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>256192</t>
+          <t>255546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>321061</t>
+          <t>322210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>595271</t>
+          <t>588594</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>657842</t>
+          <t>655194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>538189</t>
+          <t>535936</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>603471</t>
+          <t>602367</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1147155</t>
+          <t>1148095</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1239627</t>
+          <t>1241972</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>223938</t>
+          <t>226002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>278814</t>
+          <t>281254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>287473</t>
+          <t>286573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>348173</t>
+          <t>350065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>528153</t>
+          <t>528999</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>607089</t>
+          <t>609618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82813</t>
+          <t>84067</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>123644</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,47 +6684,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>104094</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>122869</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>10,9%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>104094</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>85418</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>125842</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,29%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>181200</t>
+          <t>175985</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>237823</t>
+          <t>234474</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>490961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>540988</t>
+          <t>540745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>459163</t>
+          <t>459968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>513480</t>
+          <t>514655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>960477</t>
+          <t>959748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1041314</t>
+          <t>1039943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121894</t>
+          <t>119717</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>163395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169302</t>
+          <t>167846</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219985</t>
+          <t>217306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299524</t>
+          <t>300873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366669</t>
+          <t>366304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>221698</t>
+          <t>221434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>277274</t>
+          <t>276307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>211034</t>
+          <t>209199</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>265451</t>
+          <t>266835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>448651</t>
+          <t>446416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>530423</t>
+          <t>522274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>511955</t>
+          <t>511169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>571549</t>
+          <t>573854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>531672</t>
+          <t>531053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>598029</t>
+          <t>598290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1056454</t>
+          <t>1065024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1148933</t>
+          <t>1150905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>120611</t>
+          <t>120243</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162523</t>
+          <t>161962</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210092</t>
+          <t>211638</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>266254</t>
+          <t>268787</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>344769</t>
+          <t>344516</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>420739</t>
+          <t>415172</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>505598</t>
+          <t>502448</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>592706</t>
+          <t>591218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>503545</t>
+          <t>507561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>590770</t>
+          <t>591602</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1043913</t>
+          <t>1036004</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1163837</t>
+          <t>1166070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2019681</t>
+          <t>2011761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2137122</t>
+          <t>2133059</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1927529</t>
+          <t>1927905</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2048841</t>
+          <t>2050732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3989228</t>
+          <t>3980850</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4149508</t>
+          <t>4147983</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>701210</t>
+          <t>704061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>799716</t>
+          <t>805964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>939460</t>
+          <t>939649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1053606</t>
+          <t>1052867</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1675399</t>
+          <t>1678934</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1818983</t>
+          <t>1823928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>92041</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>73500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100995</t>
+          <t>113020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>85652</t>
+          <t>93644</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72701</t>
+          <t>79128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101602</t>
+          <t>109274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>165352</t>
+          <t>185685</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143202</t>
+          <t>161142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190684</t>
+          <t>214410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396166</t>
+          <t>420610</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372138</t>
+          <t>395297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421517</t>
+          <t>447883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>399685</t>
+          <t>434348</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379590</t>
+          <t>413524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418468</t>
+          <t>455798</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>795851</t>
+          <t>854958</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>763222</t>
+          <t>820992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>829529</t>
+          <t>887465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>158320</t>
+          <t>176801</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139110</t>
+          <t>154616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179524</t>
+          <t>200586</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>189200</t>
+          <t>203861</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>172424</t>
+          <t>186181</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>206049</t>
+          <t>223248</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>347520</t>
+          <t>380662</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>321649</t>
+          <t>354556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>374855</t>
+          <t>410765</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634186</t>
+          <t>689451</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634186</t>
+          <t>689451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634186</t>
+          <t>689451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>674537</t>
+          <t>731853</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>674537</t>
+          <t>731853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>674537</t>
+          <t>731853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1308723</t>
+          <t>1421305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1308723</t>
+          <t>1421305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1308723</t>
+          <t>1421305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>165651</t>
+          <t>182588</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80107</t>
+          <t>157077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224058</t>
+          <t>212982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>163839</t>
+          <t>181400</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145024</t>
+          <t>160369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183957</t>
+          <t>205102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>329490</t>
+          <t>363988</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212935</t>
+          <t>329433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>387312</t>
+          <t>404151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>857738</t>
+          <t>678130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>761433</t>
+          <t>639890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1040836</t>
+          <t>708871</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>576008</t>
+          <t>646393</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>550602</t>
+          <t>616315</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>599128</t>
+          <t>672852</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1433747</t>
+          <t>1324523</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1325008</t>
+          <t>1279345</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1674198</t>
+          <t>1371801</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>187008</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75542</t>
+          <t>162488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220502</t>
+          <t>213320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>218259</t>
+          <t>243045</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>197663</t>
+          <t>220734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>239139</t>
+          <t>267372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>387572</t>
+          <t>430053</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259383</t>
+          <t>396321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>448108</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047726</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047726</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2150809</t>
+          <t>2118564</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2150809</t>
+          <t>2118564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2150809</t>
+          <t>2118564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>131241</t>
+          <t>151934</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109780</t>
+          <t>128244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156312</t>
+          <t>175870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>143169</t>
+          <t>172402</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74581</t>
+          <t>153403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>195265</t>
+          <t>196669</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>274409</t>
+          <t>324337</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>171483</t>
+          <t>292967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>325458</t>
+          <t>359995</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>495262</t>
+          <t>552259</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>467270</t>
+          <t>521400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>519716</t>
+          <t>580910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>654656</t>
+          <t>490592</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>563505</t>
+          <t>463789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>791254</t>
+          <t>516755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1149918</t>
+          <t>1042852</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1067292</t>
+          <t>1003002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1324478</t>
+          <t>1082462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75833</t>
+          <t>94640</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61538</t>
+          <t>76551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92854</t>
+          <t>118009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>133353</t>
+          <t>146798</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67217</t>
+          <t>129920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179600</t>
+          <t>166477</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>209187</t>
+          <t>241439</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138121</t>
+          <t>215245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>249912</t>
+          <t>269486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>702336</t>
+          <t>798833</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>702336</t>
+          <t>798833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>702336</t>
+          <t>798833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>931178</t>
+          <t>809793</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>931178</t>
+          <t>809793</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>931178</t>
+          <t>809793</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1633514</t>
+          <t>1608627</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1633514</t>
+          <t>1608627</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1633514</t>
+          <t>1608627</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>270031</t>
+          <t>285024</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>241728</t>
+          <t>257111</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>298402</t>
+          <t>313303</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>267803</t>
+          <t>287430</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>213820</t>
+          <t>263329</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>299303</t>
+          <t>315500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>537835</t>
+          <t>572454</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>467157</t>
+          <t>534372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>578710</t>
+          <t>614296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>541161</t>
+          <t>579567</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>511264</t>
+          <t>548751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>571760</t>
+          <t>614001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>607474</t>
+          <t>600058</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>562776</t>
+          <t>568358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>708381</t>
+          <t>629650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1148635</t>
+          <t>1179626</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1100485</t>
+          <t>1132989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1254691</t>
+          <t>1220232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>111472</t>
+          <t>120081</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94070</t>
+          <t>103039</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130589</t>
+          <t>140579</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>214695</t>
+          <t>228333</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173757</t>
+          <t>207044</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>243734</t>
+          <t>252709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,27 +9928,27 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>326167</t>
+          <t>348414</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>288641</t>
+          <t>319612</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>361077</t>
+          <t>376868</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>922664</t>
+          <t>984672</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>922664</t>
+          <t>984672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>922664</t>
+          <t>984672</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1089973</t>
+          <t>1115822</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1089973</t>
+          <t>1115822</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1089973</t>
+          <t>1115822</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012637</t>
+          <t>2100494</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012637</t>
+          <t>2100494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012637</t>
+          <t>2100494</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>506288</t>
+          <t>657160</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>714052</t>
+          <t>764457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>534566</t>
+          <t>693606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>724014</t>
+          <t>780144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1142504</t>
+          <t>1381434</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1412003</t>
+          <t>1517799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2180364</t>
+          <t>2169774</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2546506</t>
+          <t>2296031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2123130</t>
+          <t>2119928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2513248</t>
+          <t>2227481</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401958</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4342465</t>
+          <t>4321951</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4870359</t>
+          <t>4480650</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>400690</t>
+          <t>535058</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>574038</t>
+          <t>623416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>616359</t>
+          <t>777850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>820730</t>
+          <t>863139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1099221</t>
+          <t>1341891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1372437</t>
+          <t>1457889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
